--- a/data/trans_dic/ProbViv_temp-Clase-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_temp-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas de temperatura en la vivienda</t>
+          <t>Población con problemas de temperatura, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,07; 43,99</t>
+          <t>35,62; 44,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,09; 37,25</t>
+          <t>29,19; 36,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33,73; 39,82</t>
+          <t>33,72; 39,71</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,59; 42,89</t>
+          <t>33,59; 42,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,58; 45,18</t>
+          <t>36,38; 44,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,37; 42,45</t>
+          <t>35,79; 42,28</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,06; 43,89</t>
+          <t>10,64; 44,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,33; 47,55</t>
+          <t>34,76; 47,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,7; 43,36</t>
+          <t>13,56; 43,24</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,23; 40,54</t>
+          <t>34,21; 40,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,95; 35,63</t>
+          <t>16,1; 35,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,54; 36,89</t>
+          <t>22,34; 37,04</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>38,96; 48,73</t>
+          <t>39,75; 49,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42,84; 62,47</t>
+          <t>42,78; 61,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42,99; 56,32</t>
+          <t>42,82; 57,01</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30,84; 50,91</t>
+          <t>30,89; 50,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38,4; 45,11</t>
+          <t>38,6; 45,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38,2; 45,24</t>
+          <t>38,37; 45,18</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,67; 40,27</t>
+          <t>29,57; 40,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,41; 41,95</t>
+          <t>31,64; 42,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32,87; 40,72</t>
+          <t>32,6; 40,24</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas de temperatura en la vivienda</t>
+          <t>Población con problemas de temperatura, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>177158; 222257</t>
+          <t>179979; 223223</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>130154; 166674</t>
+          <t>130628; 163206</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>321331; 379316</t>
+          <t>321204; 378347</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>151885; 193932</t>
+          <t>151919; 192057</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>139958; 172851</t>
+          <t>139178; 171493</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>303650; 354336</t>
+          <t>298796; 352946</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>67201; 293331</t>
+          <t>71073; 296938</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58975; 79367</t>
+          <t>58017; 78850</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>106084; 362131</t>
+          <t>113209; 361097</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>354174; 419543</t>
+          <t>354005; 420271</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>136469; 348480</t>
+          <t>157429; 347186</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>473850; 742613</t>
+          <t>449761; 745620</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>185074; 231479</t>
+          <t>188832; 233608</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>360459; 525563</t>
+          <t>359905; 519536</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>565867; 741402</t>
+          <t>563664; 750451</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>74174; 122444</t>
+          <t>74301; 121288</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>292380; 343469</t>
+          <t>293862; 344817</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>382767; 453255</t>
+          <t>384469; 452647</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>967956; 1359546</t>
+          <t>998447; 1364518</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1123831; 1500755</t>
+          <t>1131886; 1510747</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2285701; 2831745</t>
+          <t>2266915; 2798077</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/ProbViv_temp-Clase-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_temp-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>37,6%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,62; 44,18</t>
+          <t>36,45; 44,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,19; 36,47</t>
+          <t>30,4; 37,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33,72; 39,71</t>
+          <t>34,74; 40,82</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>40,31%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,59; 42,47</t>
+          <t>34,64; 43,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,38; 44,83</t>
+          <t>37,36; 45,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,79; 42,28</t>
+          <t>36,95; 43,67</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>42,1%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,64; 44,43</t>
+          <t>37,16; 46,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,76; 47,24</t>
+          <t>34,9; 47,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,56; 43,24</t>
+          <t>38,3; 45,64</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,21; 40,61</t>
+          <t>36,08; 42,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,1; 35,5</t>
+          <t>33,63; 39,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,34; 37,04</t>
+          <t>35,72; 39,92</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,34%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>39,75; 49,18</t>
+          <t>41,42; 51,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42,78; 61,75</t>
+          <t>45,14; 50,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42,82; 57,01</t>
+          <t>45,05; 49,8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>44,28%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30,89; 50,43</t>
+          <t>35,08; 55,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38,6; 45,29</t>
+          <t>40,87; 47,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38,37; 45,18</t>
+          <t>40,68; 47,55</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>41,39%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>29,57; 40,42</t>
+          <t>39,57; 43,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,64; 42,23</t>
+          <t>40,06; 42,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32,6; 40,24</t>
+          <t>40,22; 42,69</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>201361</t>
+          <t>222927</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>146876</t>
+          <t>167762</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>348237</t>
+          <t>390689</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>179979; 223223</t>
+          <t>200687; 246377</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>130628; 163206</t>
+          <t>148490; 185113</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>321204; 378347</t>
+          <t>360947; 424097</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>172867</t>
+          <t>189659</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>155483</t>
+          <t>175693</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>328349</t>
+          <t>365352</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>151919; 192057</t>
+          <t>167362; 211475</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>139178; 171493</t>
+          <t>158070; 193356</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>298796; 352946</t>
+          <t>334915; 395810</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>181793</t>
+          <t>199970</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>68158</t>
+          <t>77522</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>249952</t>
+          <t>277491</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>71073; 296938</t>
+          <t>175241; 221020</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58017; 78850</t>
+          <t>65434; 88598</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>113209; 361097</t>
+          <t>252438; 300819</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>386613</t>
+          <t>442410</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>268335</t>
+          <t>312536</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>654947</t>
+          <t>754946</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>354005; 420271</t>
+          <t>408416; 478680</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>157429; 347186</t>
+          <t>289665; 336194</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>449761; 745620</t>
+          <t>711992; 795616</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>208986</t>
+          <t>262060</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>413618</t>
+          <t>400097</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>622604</t>
+          <t>662158</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>188832; 233608</t>
+          <t>235264; 290869</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>359905; 519536</t>
+          <t>375084; 422261</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>563664; 750451</t>
+          <t>630198; 696592</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>98582</t>
+          <t>107827</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>318153</t>
+          <t>371015</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>416734</t>
+          <t>478841</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>74301; 121288</t>
+          <t>83212; 131141</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>293862; 344817</t>
+          <t>345033; 399814</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>384469; 452647</t>
+          <t>440011; 514308</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1250201</t>
+          <t>1424852</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1370623</t>
+          <t>1504625</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2620824</t>
+          <t>2929477</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>998447; 1364518</t>
+          <t>1362078; 1489693</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1131886; 1510747</t>
+          <t>1456487; 1558889</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2266915; 2798077</t>
+          <t>2847053; 3021804</t>
         </is>
       </c>
     </row>
